--- a/exports/xlsx/terms_definition_2.xlsx
+++ b/exports/xlsx/terms_definition_2.xlsx
@@ -456,7 +456,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ancillary Data</t>
+          <t>Verification</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -464,28 +464,27 @@
           <t>- core
 - to be approved
 - calval ingest
-- WGISS
 - WGCV</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Non-instrument data required for processing, including orbit, attitude, time, spacecraft engineering, calibration, quality, and external model data.</t>
+          <t>Evaluation of whether a product, service, or system complies with a regulation, specification, or imposed condition.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>- CEOS-ARD PFS template 20220302</t>
+          <t>- EU-US Land Imaging EO Collaboration</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Stability</t>
+          <t>Validation</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -493,43 +492,46 @@
           <t>- core
 - to be approved
 - calval ingest
-- WGISS
 - WGCV</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Property of a measuring instrument, whereby its metrological properties remain constant in time</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
+          <t>Process of verifying that specified requirements are met by comparing mission products with representative reference data, ensuring quality and traceability.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>- In this part of ISO 19159, the term validation is used in a limited sense and only relates to the validation of calibration data in order to control their change over time.</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>- VIM/ISO:99 [ [RD18](https://www.bipm.org/en/publications/guides/vim.html) ]</t>
+          <t>- BIPM; QA4EO; ESA?, modified</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Latency</t>
+          <t>Information</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>- core
-- to be discussed
-- calval ingest
-- WGCV
-- WGClimate</t>
+          <t>- base
+- to be approved
+- calval ingest
+- WGISS
+- WGCV</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Time delay between event occurrence and use of processed data, typically within 3 hours for meteorological purposes.</t>
+          <t>Knowledge exchangeable in the form of data, including representation information that enables interpretation of the data.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -543,37 +545,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Application Programming Interface</t>
+          <t>Uncertainty</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>- core
-- to be discussed
-- calval ingest
-- WGISS
-- WGCV</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
+- to be approved
+- calval ingest
+- WGCV</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>A set of functions and procedures allowing the creation of applications that access the features or data of an operating system, application, or other service.</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>An application programming interface (API) is an interface that defines interactions between multiple software applications or mixed hardware-software intermediaries. It defines the kinds of calls or requests that can be made, how to make them, the data formats that should be used, the conventions to follow, etc. It can also provide extension mechanisms so that users can extend existing functionality in various ways and to varying degrees. An API can be entirely custom, specific to a component, or designed based on an industry-standard to ensure interoperability. Through information hiding, APIs enable modular programming, allowing users to use the interface independently of the implementation.</t>
-        </is>
-      </c>
+          <t>Parameter, associated with the result of a measurement, that characterises the dispersion of the values that could reasonably be attributed to the measurand.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>- CEOS CalVal Portal</t>
+          <t>- GUM</t>
         </is>
       </c>
     </row>
@@ -586,7 +579,9 @@
       <c r="B6" t="inlineStr">
         <is>
           <t>- base
-- to be discussed</t>
+- to be discussed
+- WGISS
+- WGCV</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
@@ -610,37 +605,29 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Subscription</t>
+          <t>Source Data</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>- core
-- to be discussed
+- to be approved
 - calval ingest
 - WGISS
 - WGCV</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Standing Order</t>
-        </is>
-      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Email issued to users when new data is available from the CLASS infrastructure.</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>An email provides a 'symbolic link' to new files stored in an access area. (Not sure if all 'links' are emailed or some other notification)</t>
-        </is>
-      </c>
+          <t>Unprocessed data not yet transformed into meaningful information, originating from the source location in computing systems.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>- [OSGS/CLASS - NCEI/DAB](https://calvalportal.ceos.org/web/guest/t-d_wiki?p_p_id=com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn&amp;p_p_lifecycle=0&amp;p_p_state=normal&amp;p_p_mode=view&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_mvcRenderCommandName=%2Fwiki%2Fedit_page&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_redirect=https%3A%2F%2Fcalvalportal.ceos.org%2Fweb%2Fguest%2Ft-d_wiki%3Fp_p_id%3Dcom_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn%26p_p_lifecycle%3D0%26p_p_state%3Dnormal%26p_p_mode%3Dview%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_mvcRenderCommandName%3D%252Fwiki%252Fview_page%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_nodeName%3DCEOS_Terms_and_Definitions%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_title%3DStanding%2BOrder%2B%2528Subscription%2529&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_nodeId=668236&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_title=OSGS%2FCLASS+-+NCEI%2FDAB)
+          <t>- multiple sources needs revision
 - NESDIS Data Management Lexicon and Related Terms</t>
         </is>
       </c>
@@ -648,44 +635,41 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Georectifying</t>
+          <t>Latency</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>- core
-- to be discussed</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Orthorectifying</t>
-        </is>
-      </c>
+- to be discussed
+- calval ingest
+- WGISS</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>The correction of sample locations to achieve some sort of geometric regularity, e.g., a regular 2D geographic grid.</t>
+          <t>Time delay between event occurrence and use of processed data, typically within 3 hours for meteorological purposes.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- [CEOS/WGISS/DSIG/GLOS](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Standard Uncertainty</t>
+          <t>Entity</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>- core
-- to be approved
-- calval ingest
+          <t>- base
+- to be approved
 - WGISS
 - WGCV</t>
         </is>
@@ -693,85 +677,93 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Measurement uncertainty expressed as a standard deviation</t>
+          <t>Government or business organization that is formed to conduct business or represent the government of the day.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>CEOS Entities include Working Groups, Virtual Constellations, etc.</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>- VIM/ISO:99 [ [RD18](https://www.bipm.org/en/publications/guides/vim.html) ]</t>
+          <t>- WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Verification</t>
+          <t>Georectifying</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>- core
-- to be approved
-- calval ingest
-- WGCV
-- WGISS</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
+- to be discussed
+- LSI-VC
+- WGCV</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Orthorectifying</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Evaluation of whether a product, service, or system complies with a regulation, specification, or imposed condition.</t>
+          <t>The correction of sample locations to achieve some sort of geometric regularity, e.g., a regular 2D geographic grid.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>- EU-US Land Imaging EO Collaboration</t>
+          <t>- KCEO</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Quality Indicator</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>- core
-- to be approved
-- calval ingest
-- WGISS
+- to be discussed
+- calval ingest
 - WGCV</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Information provided as a number, set of numbers, graph, uncertainty budget, or flag to evaluate data fitness for purpose.</t>
+          <t>Device which transmits an output signal in response to a physical input stimulus as voltage. In Earth observation a distinction between passives sensors, such as radiometers, and active sensors, such as radars, is common. Earth observation sensors – or instruments – are operated from different ground-/water-based, airborne, or spaceborne platforms.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>- [CEOS/WGISS/DSIG/GLOS](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+          <t>- [CEOS/WGISS/DSIG/GLOS](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)
+- [CEOS EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)
+- NESDIS Data Management Lexicon and Related Terms</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Property</t>
+          <t>Collection</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>- base
-- to be discussed
+          <t>- core
+- to be approved
 - calval ingest
 - WGISS
 - WGCV</t>
@@ -780,21 +772,28 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Assessable and attributable characteristic of a phenomenon, named and either observable (factual) or assigned (fictional).</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
+          <t>Grouping of environmental data or products sharing common characteristics, represented by a single metadata record and consisting of one or more granules; also referred to as a dataset.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Note that in these definitions of “collection” and “granule” that a collection is the minimum citable unit of data, akin to a journal article. This approach helps align data citation and publication with the much more mature practices surrounding journal article publication. In this alignment, granules can be thought of as the words in that article. This functional definition allows for flexibility as well; just as current science domains have their own standards for what qualifies as a minimally citable body of work that can go into a single journal article, different data domains across NOAA can do the same and determine what makes sense to go into one of their collections. If NOAA should ever reach a more detailed definition, adjustments can be made to align the collection metadata with that new definition.</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>- CEOS CalVal Portal</t>
+          <t>- [CEOS/WGISS/DSIG/GLOS](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)
+- [ESA PDGS Glossary, PGSI-GSEG-EOPG-LI-13-0033 (MM-PDGS Glossary Issue 2.0_forReview.docx)](https://calvalportal.ceos.org/web/guest/t-d_wiki?p_p_id=com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn&amp;p_p_lifecycle=0&amp;p_p_state=normal&amp;p_p_mode=view&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_mvcRenderCommandName=%2Fwiki%2Fedit_page&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_redirect=https%3A%2F%2Fcalvalportal.ceos.org%2Fweb%2Fguest%2Ft-d_wiki%3Fp_p_id%3Dcom_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn%26p_p_lifecycle%3D0%26p_p_state%3Dnormal%26p_p_mode%3Dview%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_mvcRenderCommandName%3D%252Fwiki%252Fview_page%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_nodeName%3DCEOS_Terms_and_Definitions%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_title%3DCollection&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_nodeId=668236&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_title=ESA+PDGS+Glossary%2C+PGSI-GSEG-EOPG-LI-13-0033+%28MM-PDGS+Glossary+Issue+2.0_forReview.docx%29)
+- This term and functional definition emerged from an ESIP session on collections and granules in the mid-2010’s.; [Reference Model for an Open Archival Information System (OAIS), Recommended Practice CCSDS 650.0-M-2, Magenta Book 2012](https://public.ccsds.org/pubs/650x0m2.pdf)
+- NESDIS Data Management Lexicon and Related Terms</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Validation</t>
+          <t>Auxiliary Data</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -802,58 +801,65 @@
           <t>- core
 - to be approved
 - calval ingest
-- WGCV
-- WGClimate</t>
+- WGISS
+- WGCV</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Process of verifying that specified requirements are met by comparing mission products with representative reference data, ensuring quality and traceability.</t>
+          <t>Data required to perform processing of Sensor Data which is not obtained from the Sensor itself. Includes: (a) Data provided by the spacecraft (e.g. orbit Position and velocity, attitude, instrument house-keeping Data, on-board time); (b) Data not available from on-board sources.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>- In this part of ISO 19159, the term validation is used in a limited sense and only relates to the validation of calibration data in order to control their change over time.</t>
+          <t>For EnMAP, this includes (a) orbit files, attitude files, Calibration Data, instrument house-keeping Data; (b) atmospheric parameters, reference images.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>- BIPM; QA4EO; ESA?, modified</t>
+          <t>- ENMAP Glossary of Terms, https://www.enmap.org/Data/doc/EnMAP_Terms.pdf, 20210624
+- EO Data Stewardship Glossary</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Geolocating</t>
+          <t>Accuracy</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>- core
-- to be approved</t>
+- to be approved
+- calval ingest
+- WGCV</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Determination of the geographic location of a feature of two or more dimensions.</t>
+          <t>Closeness of agreement between a measured quantity value and a true quantity value of a measurand.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>- ISO 19130-1:2018, 3.36 ('geopositioning'), modified</t>
+          <t>- VIM [ [RD18](https://www.bipm.org/en/publications/guides/vim.html) ], GUM [ [RD4](https://www.bipm.org/utils/common/documents/jcgm/JCGM_100_2008_E.pdf) ]
+- Definitions used in other communities
+- ACIX community
+- [Community, not standard, definition]
+- Used in the atmospheric correction community to represent the average difference between the modelled and measured quantities</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sensor</t>
+          <t>Application Programming Interface</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -861,50 +867,141 @@
           <t>- core
 - to be discussed
 - calval ingest
-- WGCV
-- WGClimate</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
+- WGISS</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Device which transmits an output signal in response to a physical input stimulus as voltage. In Earth observation a distinction between passives sensors, such as radiometers, and active sensors, such as radars, is common. Earth observation sensors – or instruments – are operated from different ground-/water-based, airborne, or spaceborne platforms.</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
+          <t>A set of functions and procedures allowing the creation of applications that access the features or data of an operating system, application, or other service.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>An application programming interface (API) is an interface that defines interactions between multiple software applications or mixed hardware-software intermediaries. It defines the kinds of calls or requests that can be made, how to make them, the data formats that should be used, the conventions to follow, etc. It can also provide extension mechanisms so that users can extend existing functionality in various ways and to varying degrees. An API can be entirely custom, specific to a component, or designed based on an industry-standard to ensure interoperability. Through information hiding, APIs enable modular programming, allowing users to use the interface independently of the implementation.</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>- [CEOS/WGISS/DSIG/GLOS](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)
-- [CEOS EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)
-- NESDIS Data Management Lexicon and Related Terms</t>
+          <t>- CEOS CalVal Portal</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Calibration</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>- core
-- to be approved
-- calval ingest
-- WGCV
-- WGClimate</t>
+- source missing
+- to be discussed
+- calval ingest
+- WGCV</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Output of an organization distributable to users without transaction, derived from instrument data via processing with ancillary data, and may include metadata and browse images.</t>
+          <t>Operation that establishes and applies a relation between measurement standard values and instrument indications to derive measurement results.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
+        <is>
+          <t>- (1) CEOS/ISO:19159 [RD10]: ISO/TS 19159-1:2014(en), Geographic information - Calibration and validation of remote sensing imagery sensors and data — Part 1: Optical sensors
+- (2) VIM/ISO:99 [ [RD18](https://www.bipm.org/en/publications/guides/vim.html) ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>- core
+- to be approved
+- calval ingest
+- WGClimate
+- WGCV</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Property of a measuring instrument, whereby its metrological properties remain constant in time</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>- VIM/ISO:99 [ [RD18](https://www.bipm.org/en/publications/guides/vim.html) ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>- core
+- to be discussed
+- WGCV</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Sort of data acquired with an Uncertainty significantly lower (quantify?) than that of the data it is being compared with.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>- VIM?, modified</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>- core
+- to be approved
+- calval ingest
+- WGISS
+- WGCV</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Output of an organization distributable to users without transaction, derived from instrument data via processing with ancillary data, and may include metadata and browse images.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
         <is>
           <t>- ISO:9000 [ [RD7](https://www.iso.org/standard/45481.html) ]
 - RD7: ISO 9000:2015(en), Quality management systems - Fundamentals and vocabulary
@@ -913,20 +1010,382 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Standard Uncertainty</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>- core
+- to be approved
+- calval ingest
+- WGCV</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Measurement uncertainty expressed as a standard deviation</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>- VIM/ISO:99 [ [RD18](https://www.bipm.org/en/publications/guides/vim.html) ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>- base
+- to be approved
+- calval ingest
+- WGCV</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Property whose instances can be compared by ratio or only by order.</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>- gEOGlos (VIM4 Notes omitted)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Metadata</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>- core
+- to be approved
+- calval ingest
+- WGISS</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Data describing characteristics, content, and utility of a dataset to enable search, discovery, and access management, particularly for Earth Observation resources.</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>- WMO [ [RD19](http://www.bom.gov.au/wmo/quality_management.shtml) ]
+- [Reference Model for an Open Archival Information System (OAIS), Recommended Practice CCSDS 650.0-M-2, Magenta Book 2012](https://public.ccsds.org/pubs/650x0m2.pdf) ; [CEOS EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)
+- NESDIS Data Management Lexicon and Related Terms</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>- core
+- to be approved
+- WGCV
+- WGISS</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Source data that has been processed to a common set of requirements and organised into a form that allows immediate analysis and interoperability through time and with other collections.</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>- WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Ancillary Data</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>- core
+- to be approved
+- calval ingest
+- WGISS
+- WGCV</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Non-instrument data required for processing, including orbit, attitude, time, spacecraft engineering, calibration, quality, and external model data.</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>- CEOS-ARD PFS template 20220302</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>- base
+- to be approved
+- calval ingest
+- WGISS
+- WGCV</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Scientific or technical measurements, calculated values, observations, or facts representable by numbers, tables, graphs, models, text, or symbols and used as a basis for reasoning and calculation.</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>- WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data
+- [CEOS/WGISS/DSIG/GLOS](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)
+- [CEOS-WGISS Document: Auxiliary Data in the CEOS Community: Reference Guidelines Document Part 1: Current Usage (1996) accessible at wgiss.ceos.org/archive/archive.doc/ads200part1.doc](https://calvalportal.ceos.org/web/guest/t-d_wiki?p_p_id=com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn&amp;p_p_lifecycle=0&amp;p_p_state=normal&amp;p_p_mode=view&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_mvcRenderCommandName=%2Fwiki%2Fedit_page&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_redirect=https%3A%2F%2Fcalvalportal.ceos.org%2Fweb%2Fguest%2Ft-d_wiki%3Fp_p_id%3Dcom_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn%26p_p_lifecycle%3D0%26p_p_state%3Dnormal%26p_p_mode%3Dview%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_mvcRenderCommandName%3D%252Fwiki%252Fview_page%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_nodeName%3DCEOS_Terms_and_Definitions%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_title%3DData&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_nodeId=668236&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_title=CEOS-WGISS+Document%3A+Auxiliary+Data+in+the+CEOS+Community%3A+Reference+Guidelines+Document+Part+1%3A+Current+Usage+%281996%29+accessible+at+wgiss.ceos.org%2Farchive%2Farchive.doc%2Fads200part1.doc)
+- [CEOS EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf) ; [Reference Model for an Open Archival Information System (OAIS), Recommended Practice CCSDS 650.0-M-2, Magenta Book 2012](https://public.ccsds.org/pubs/650x0m2.pdf)
+- NESDIS Data Management Lexicon and Related Terms</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Subscription</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>- core
+- to be discussed
+- calval ingest
+- WGISS</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Standing Order</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Email issued to users when new data is available from the CLASS infrastructure.</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>An email provides a 'symbolic link' to new files stored in an access area. (Not sure if all 'links' are emailed or some other notification)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>- [OSGS/CLASS - NCEI/DAB](https://calvalportal.ceos.org/web/guest/t-d_wiki?p_p_id=com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn&amp;p_p_lifecycle=0&amp;p_p_state=normal&amp;p_p_mode=view&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_mvcRenderCommandName=%2Fwiki%2Fedit_page&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_redirect=https%3A%2F%2Fcalvalportal.ceos.org%2Fweb%2Fguest%2Ft-d_wiki%3Fp_p_id%3Dcom_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn%26p_p_lifecycle%3D0%26p_p_state%3Dnormal%26p_p_mode%3Dview%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_mvcRenderCommandName%3D%252Fwiki%252Fview_page%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_nodeName%3DCEOS_Terms_and_Definitions%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_title%3DStanding%2BOrder%2B%2528Subscription%2529&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_nodeId=668236&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_title=OSGS%2FCLASS+-+NCEI%2FDAB)
+- NESDIS Data Management Lexicon and Related Terms</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Geolocating</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>- core
+- to be approved
+- WGCV</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Determination of the geographic location of a feature of two or more dimensions.</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>- ISO 19130-1:2018, 3.36 ('geopositioning'), modified</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Temporal Resolution</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>- core
+- controversial
+- to be approved
+- calval ingest
+- WGCV</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>A time period during which data was collected or observations made, or a time period that an activity or collection is linked to intellectually or thematically, for example, 1997 to 1998; the 18th century.</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>- [Australian National Data Service - Content Providers Guide - Spatial and Temporal Coverage](https://documentation.ands.org.au/display/DOC/Temporal+coverage)
+- NESDIS Data Management Lexicon and Related Terms</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Instrument Data</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>- core
+- to be approved
+- calval ingest
+- WGCV
+- WGISS</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Sensor Data, Sensor Data Record</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Data created by an instrument including scientific measurements and any engineering or ancillary data which may be included in the data packets.</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Representativeness</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>- core
+- to be approved
+- calval ingest
+- WGCV</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>The extent to which a set of measurements taken in a given space-time domain reflect the actual conditions in the same or different space-time domain taken on a scale appropriate for a specific application</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>- Nappo [RD14]
+- RD14: Nappo, C.J., Caneill J.Y., Furman R.W., Gifford F.A., Kaimal J.C., Kramer M.L., Lockhart T.J., Pendergast M.M, Pielke R.A., Randerson D., Shreffler J.H., and Wyngaard J.C., The Workshop on the Representativeness of Meteorological Observations, June 1981, Boulder, CO, Bull. Am. Meteorol. Soc. 63, 761-764, 1982.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Quality Indicator</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>- core
+- to be approved
+- calval ingest
+- WGCV</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Information provided as a number, set of numbers, graph, uncertainty budget, or flag to evaluate data fitness for purpose.</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>- [CEOS/WGISS/DSIG/GLOS](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>Phenomenon</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>- base
-- to be approved</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
+- to be approved
+- WGISS
+- WGCV</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
         <is>
           <t>A phenomenon is a fact or event that has
 properties
@@ -935,98 +1394,135 @@
 modified after Wikipedia and The Columbia Encyclopedia 2008</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
         <is>
           <t>- CEOS CalVal Portal</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Calibration</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>- core
-- source missing
-- to be discussed
-- calval ingest
-- WGISS
-- WGCV</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Operation that establishes and applies a relation between measurement standard values and instrument indications to derive measurement results.</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>- (1) CEOS/ISO:19159 [RD10]: ISO/TS 19159-1:2014(en), Geographic information - Calibration and validation of remote sensing imagery sensors and data — Part 1: Optical sensors
-- (2) VIM/ISO:99 [ [RD18](https://www.bipm.org/en/publications/guides/vim.html) ]</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Information</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>- base
-- to be approved
-- calval ingest
-- WGISS
-- WGCV</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Knowledge exchangeable in the form of data, including representation information that enables interpretation of the data.</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>- [CEOS/WGISS/DSIG/GLOS](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Preservation</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>- core
+- to be approved
+- calval ingest
+- WGISS</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Processes ensuring the technical and intellectual survival of space data sets and metadata over time, preserving integrity, discoverability, accessibility, and long-term reusability.</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Preservation covers all processes and operations on individual or multi-mission data sets for ensuring the technical and intellectual survival of Space Data set and their metadata through time. It grants dataset integrity, its discoverability and accessibility, and facilitates its (re)-use in the long term. Preservation is one of the tasks of data curation. Examples are data record improvement and consolidation. XX</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>- [CEOS/WGISS/DSIG/GLOS](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)
+- [Reference Model for an Open Archival Information System (OAIS), Recommended Practice CCSDS 650.0-M-2, Magenta Book 2012](https://public.ccsds.org/pubs/650x0m2.pdf) ; [CEOS EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)
+- NESDIS Data Management Lexicon and Related Terms</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Reproducibility</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>- core
+- to be approved
+- calval ingest
+- WGCV
+- WGISS</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Measurement precision under conditions including different locations, operators, measuring systems, and replicate measurements on similar objects.</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>- VIM/ISO:99 [ [RD18](https://www.bipm.org/en/publications/guides/vim.html) ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>- core
+- to be approved
+- calval ingest
+- WGCapD</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>External person, institution, or system consuming provided services.</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>- Includes Data Access or Science and Service Exploitation Platforms provided by a payload data ground segment.</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>- EO Data Stewardship Glossary
+- [CEOS/WGISS/DSIG/GLOS](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)
+- [CEOS EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)
+- NESDIS Data Management Lexicon and Related Terms</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>Resolution</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>- core
 - to be defined
 - calval ingest
-- WGCV
-- WGClimate</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr">
+- WGCV</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
         <is>
           <t>Smallest change in energy detectable and representable by the number of bits per pixel, where each bit doubles the number of possible values.</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
         <is>
           <t>- (1) VIM/ISO:99 [ [RD18](https://www.bipm.org/en/publications/guides/vim.html) ]; (2) NIST [RD15]; (3) MACC [RD13]
 - RD15: Prokhorov, A. V., R. U. Datla, V. P. Zakharenkov, V. Privalsky, T. W. Humpherys, and V. I. Sapritsky, Spaceborne Optoelectronic Sensors and their Radiometric Calibration. Terms and Definitions. Part 1. Calibration Techniques, Ed. by A. C. Parr and L. K. Issaev, NIST Technical Note NISTIR 7203, March 2005
@@ -1036,512 +1532,16 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>- core
-- to be approved</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Source data that has been processed to a common set of requirements and organised into a form that allows immediate analysis and interoperability through time and with other collections.</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>- WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Uncertainty</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>- core
-- to be approved
-- calval ingest
-- WGCV
-- WGISS</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Parameter, associated with the result of a measurement, that characterises the dispersion of the values that could reasonably be attributed to the measurand.</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>- GUM</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Representativeness</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>- core
-- to be approved
-- calval ingest
-- WGISS
-- WGCV</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>The extent to which a set of measurements taken in a given space-time domain reflect the actual conditions in the same or different space-time domain taken on a scale appropriate for a specific application</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>- Nappo [RD14]
-- RD14: Nappo, C.J., Caneill J.Y., Furman R.W., Gifford F.A., Kaimal J.C., Kramer M.L., Lockhart T.J., Pendergast M.M, Pielke R.A., Randerson D., Shreffler J.H., and Wyngaard J.C., The Workshop on the Representativeness of Meteorological Observations, June 1981, Boulder, CO, Bull. Am. Meteorol. Soc. 63, 761-764, 1982.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Data</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>- base
-- to be approved
-- calval ingest
-- WGISS
-- WGCV</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Scientific or technical measurements, calculated values, observations, or facts representable by numbers, tables, graphs, models, text, or symbols and used as a basis for reasoning and calculation.</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>- WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data
-- [CEOS/WGISS/DSIG/GLOS](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)
-- [CEOS-WGISS Document: Auxiliary Data in the CEOS Community: Reference Guidelines Document Part 1: Current Usage (1996) accessible at wgiss.ceos.org/archive/archive.doc/ads200part1.doc](https://calvalportal.ceos.org/web/guest/t-d_wiki?p_p_id=com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn&amp;p_p_lifecycle=0&amp;p_p_state=normal&amp;p_p_mode=view&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_mvcRenderCommandName=%2Fwiki%2Fedit_page&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_redirect=https%3A%2F%2Fcalvalportal.ceos.org%2Fweb%2Fguest%2Ft-d_wiki%3Fp_p_id%3Dcom_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn%26p_p_lifecycle%3D0%26p_p_state%3Dnormal%26p_p_mode%3Dview%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_mvcRenderCommandName%3D%252Fwiki%252Fview_page%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_nodeName%3DCEOS_Terms_and_Definitions%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_title%3DData&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_nodeId=668236&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_title=CEOS-WGISS+Document%3A+Auxiliary+Data+in+the+CEOS+Community%3A+Reference+Guidelines+Document+Part+1%3A+Current+Usage+%281996%29+accessible+at+wgiss.ceos.org%2Farchive%2Farchive.doc%2Fads200part1.doc)
-- [CEOS EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf) ; [Reference Model for an Open Archival Information System (OAIS), Recommended Practice CCSDS 650.0-M-2, Magenta Book 2012](https://public.ccsds.org/pubs/650x0m2.pdf)
-- NESDIS Data Management Lexicon and Related Terms</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Instrument Data</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>- core
-- to be approved
-- calval ingest
-- WGCV
-- WGClimate</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Sensor Data, Sensor Data Record</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Data created by an instrument including scientific measurements and any engineering or ancillary data which may be included in the data packets.</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Temporal Resolution</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>- core
-- controversial
-- to be approved
-- calval ingest
-- WGISS
-- WGCV</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>A time period during which data was collected or observations made, or a time period that an activity or collection is linked to intellectually or thematically, for example, 1997 to 1998; the 18th century.</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>- [Australian National Data Service - Content Providers Guide - Spatial and Temporal Coverage](https://documentation.ands.org.au/display/DOC/Temporal+coverage)
-- NESDIS Data Management Lexicon and Related Terms</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Accuracy</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>- core
-- to be approved
-- calval ingest
-- WGCV
-- WGISS</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Closeness of agreement between a measured quantity value and a true quantity value of a measurand.</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>- VIM [ [RD18](https://www.bipm.org/en/publications/guides/vim.html) ], GUM [ [RD4](https://www.bipm.org/utils/common/documents/jcgm/JCGM_100_2008_E.pdf) ]
-- Definitions used in other communities
-- ACIX community
-- [Community, not standard, definition]
-- Used in the atmospheric correction community to represent the average difference between the modelled and measured quantities</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Auxiliary Data</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>- core
-- to be approved
-- calval ingest
-- WGCV
-- WGClimate</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Data required to perform processing of Sensor Data which is not obtained from the Sensor itself. Includes: (a) Data provided by the spacecraft (e.g. orbit Position and velocity, attitude, instrument house-keeping Data, on-board time); (b) Data not available from on-board sources.</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>For EnMAP, this includes (a) orbit files, attitude files, Calibration Data, instrument house-keeping Data; (b) atmospheric parameters, reference images.</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>- ENMAP Glossary of Terms, https://www.enmap.org/Data/doc/EnMAP_Terms.pdf, 20210624
-- EO Data Stewardship Glossary</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Source Data</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>- core
-- to be approved
-- calval ingest
-- WGISS
-- WGCV</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Unprocessed data not yet transformed into meaningful information, originating from the source location in computing systems.</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>- multiple sources needs revision
-- NESDIS Data Management Lexicon and Related Terms</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Entity</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>- base
-- to be approved</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Government or business organization that is formed to conduct business or represent the government of the day.</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>CEOS Entities include Working Groups, Virtual Constellations, etc.</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>- WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>User</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>- core
-- to be approved
-- calval ingest
-- WGISS
-- WGCV</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>External person, institution, or system consuming provided services.</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>- Includes Data Access or Science and Service Exploitation Platforms provided by a payload data ground segment.</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>- EO Data Stewardship Glossary
-- [CEOS/WGISS/DSIG/GLOS](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)
-- [CEOS EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)
-- NESDIS Data Management Lexicon and Related Terms</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Collection</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>- core
-- to be approved
-- calval ingest
-- WGISS
-- WGCV</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Grouping of environmental data or products sharing common characteristics, represented by a single metadata record and consisting of one or more granules; also referred to as a dataset.</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Note that in these definitions of “collection” and “granule” that a collection is the minimum citable unit of data, akin to a journal article. This approach helps align data citation and publication with the much more mature practices surrounding journal article publication. In this alignment, granules can be thought of as the words in that article. This functional definition allows for flexibility as well; just as current science domains have their own standards for what qualifies as a minimally citable body of work that can go into a single journal article, different data domains across NOAA can do the same and determine what makes sense to go into one of their collections. If NOAA should ever reach a more detailed definition, adjustments can be made to align the collection metadata with that new definition.</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>- [CEOS/WGISS/DSIG/GLOS](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)
-- [ESA PDGS Glossary, PGSI-GSEG-EOPG-LI-13-0033 (MM-PDGS Glossary Issue 2.0_forReview.docx)](https://calvalportal.ceos.org/web/guest/t-d_wiki?p_p_id=com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn&amp;p_p_lifecycle=0&amp;p_p_state=normal&amp;p_p_mode=view&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_mvcRenderCommandName=%2Fwiki%2Fedit_page&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_redirect=https%3A%2F%2Fcalvalportal.ceos.org%2Fweb%2Fguest%2Ft-d_wiki%3Fp_p_id%3Dcom_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn%26p_p_lifecycle%3D0%26p_p_state%3Dnormal%26p_p_mode%3Dview%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_mvcRenderCommandName%3D%252Fwiki%252Fview_page%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_nodeName%3DCEOS_Terms_and_Definitions%26_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_title%3DCollection&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_nodeId=668236&amp;_com_liferay_wiki_web_portlet_WikiDisplayPortlet_INSTANCE_B9cyrDcwYNcn_title=ESA+PDGS+Glossary%2C+PGSI-GSEG-EOPG-LI-13-0033+%28MM-PDGS+Glossary+Issue+2.0_forReview.docx%29)
-- This term and functional definition emerged from an ESIP session on collections and granules in the mid-2010’s.; [Reference Model for an Open Archival Information System (OAIS), Recommended Practice CCSDS 650.0-M-2, Magenta Book 2012](https://public.ccsds.org/pubs/650x0m2.pdf)
-- NESDIS Data Management Lexicon and Related Terms</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Quantity</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>- base
-- to be approved
-- calval ingest
-- WGISS
-- WGCV</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Property whose instances can be compared by ratio or only by order.</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>- gEOGlos (VIM4 Notes omitted)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>- core
-- to be discussed</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Sort of data acquired with an Uncertainty significantly lower (quantify?) than that of the data it is being compared with.</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>- VIM?, modified</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Metadata</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>- core
-- to be approved
-- calval ingest
-- WGISS
-- WGCV</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Data describing characteristics, content, and utility of a dataset to enable search, discovery, and access management, particularly for Earth Observation resources.</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>- WMO [ [RD19](http://www.bom.gov.au/wmo/quality_management.shtml) ]
-- [Reference Model for an Open Archival Information System (OAIS), Recommended Practice CCSDS 650.0-M-2, Magenta Book 2012](https://public.ccsds.org/pubs/650x0m2.pdf) ; [CEOS EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)
-- NESDIS Data Management Lexicon and Related Terms</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Reproducibility</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>- core
-- to be approved
-- calval ingest
-- WGISS
-- WGCV</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Measurement precision under conditions including different locations, operators, measuring systems, and replicate measurements on similar objects.</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>- VIM/ISO:99 [ [RD18](https://www.bipm.org/en/publications/guides/vim.html) ]</t>
-        </is>
-      </c>
-    </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Preservation</t>
+          <t>Property</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>- core
-- to be approved
+          <t>- base
+- to be discussed
 - calval ingest
 - WGISS
 - WGCV</t>
@@ -1550,20 +1550,14 @@
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Processes ensuring the technical and intellectual survival of space data sets and metadata over time, preserving integrity, discoverability, accessibility, and long-term reusability.</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Preservation covers all processes and operations on individual or multi-mission data sets for ensuring the technical and intellectual survival of Space Data set and their metadata through time. It grants dataset integrity, its discoverability and accessibility, and facilitates its (re)-use in the long term. Preservation is one of the tasks of data curation. Examples are data record improvement and consolidation. XX</t>
-        </is>
-      </c>
+          <t>Assessable and attributable characteristic of a phenomenon, named and either observable (factual) or assigned (fictional).</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>- [CEOS/WGISS/DSIG/GLOS](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)
-- [Reference Model for an Open Archival Information System (OAIS), Recommended Practice CCSDS 650.0-M-2, Magenta Book 2012](https://public.ccsds.org/pubs/650x0m2.pdf) ; [CEOS EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)
-- NESDIS Data Management Lexicon and Related Terms</t>
+          <t>- CEOS CalVal Portal</t>
         </is>
       </c>
     </row>
